--- a/data/附件1：样例数据.xlsx
+++ b/data/附件1：样例数据.xlsx
@@ -1133,7 +1133,7 @@
   <dimension ref="A1:AK1001"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="24" max="24" width="32" customWidth="1"/>
+    <col min="24" max="24" width="38.5454545454545" customWidth="1"/>
     <col min="25" max="26" width="25.4545454545455" customWidth="1"/>
     <col min="27" max="28" width="17.0909090909091" customWidth="1"/>
     <col min="32" max="32" width="21.7272727272727" customWidth="1"/>
